--- a/Kakashi_RP_audits_bundle_by_GPT5_6/NARUTO_CHRONOLOGY_RECONCILIATION.xlsx
+++ b/Kakashi_RP_audits_bundle_by_GPT5_6/NARUTO_CHRONOLOGY_RECONCILIATION.xlsx
@@ -13212,7 +13212,7 @@
         <x:v>K54–K55</x:v>
       </x:c>
       <x:c r="E27" s="40" t="str">
-        <x:v>Какаші, Міката, Тензо й Ґенма: місія в шахтах Іви.</x:v>
+        <x:v>Какаші, Токара, Тензо й Ґенма: місія в шахтах Іви.</x:v>
       </x:c>
       <x:c r="F27" s="40" t="str">
         <x:v>Ґенма має 42–43 дні від Танікави; ім’я Ямато замінене.</x:v>
